--- a/artfynd/A 22069-2023 artfynd.xlsx
+++ b/artfynd/A 22069-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22069-2023 artfynd.xlsx
+++ b/artfynd/A 22069-2023 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15102229</v>
+        <v>15102224</v>
       </c>
       <c r="B2" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550892.3054449243</v>
+        <v>550752</v>
       </c>
       <c r="R2" t="n">
-        <v>6731112.197243514</v>
+        <v>6731326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,24 +762,9 @@
           <t>2012-07-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-07-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flygande i kanten mot skogen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,7 +778,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Ängsmark.</t>
+          <t>Fuktig mark.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -820,19 +800,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15102224</v>
+        <v>15102225</v>
       </c>
       <c r="B3" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -855,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -879,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550752.4866058432</v>
+        <v>550763</v>
       </c>
       <c r="R3" t="n">
-        <v>6731325.598807146</v>
+        <v>6731257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -912,19 +887,9 @@
           <t>2012-07-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-07-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,7 +903,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Fuktig mark.</t>
+          <t>Ängsmark.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -960,19 +925,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15102225</v>
+        <v>15102229</v>
       </c>
       <c r="B4" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -995,7 +955,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1019,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550763.2675455695</v>
+        <v>550892</v>
       </c>
       <c r="R4" t="n">
-        <v>6731256.732142512</v>
+        <v>6731112</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1052,19 +1012,14 @@
           <t>2012-07-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-07-03</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flygande i kanten mot skogen.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 22069-2023 artfynd.xlsx
+++ b/artfynd/A 22069-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Falu kommun inventering ansvarsarter</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15102224</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>Falu kommun inventering ansvarsarter</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15102225</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1052,8 +1067,18 @@
           <t>Falu kommun inventering ansvarsarter</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15102229</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>